--- a/sheets/대금율보/검수/울지마라 가야금아.xlsx
+++ b/sheets/대금율보/검수/울지마라 가야금아.xlsx
@@ -4175,11 +4175,7 @@
           <t xml:space="preserve">줄을</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H4" s="21"/>
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
@@ -4261,8 +4257,7 @@
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
@@ -4277,18 +4272,14 @@
         </is>
       </c>
       <c r="I6" s="24"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –林</t>
         </is>
       </c>
@@ -4397,7 +4388,7 @@
       <c r="C9" s="23"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –汰</t>
         </is>
       </c>
@@ -4408,7 +4399,7 @@
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢‹
+          <t xml:space="preserve">潢潢
 –汰</t>
         </is>
       </c>
@@ -4467,11 +4458,7 @@
           <t xml:space="preserve">르고</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -4539,7 +4526,7 @@
       <c r="E12" s="23"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰汰‹
+          <t xml:space="preserve">汰汰
 –無</t>
         </is>
       </c>
@@ -4579,7 +4566,7 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 汰</t>
         </is>
       </c>
@@ -4661,7 +4648,7 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –無</t>
         </is>
       </c>
@@ -4806,7 +4793,7 @@
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林‹
+          <t xml:space="preserve">南林
 –夾</t>
         </is>
       </c>
@@ -4841,8 +4828,7 @@
       <c r="F19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -4895,7 +4881,7 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 夾太</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/울지마라 가야금아.xlsx
+++ b/sheets/대금율보/검수/울지마라 가야금아.xlsx
@@ -4061,22 +4061,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="76.92" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="68.77" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="68.77" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="68.77" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="68.77" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
       <c r="J6" s="21"/>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="68.77" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="68.77" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="68.77" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="68.77" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="68.77" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="25" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="68.77" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="25" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="68.77" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="25" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="68.77" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="68.77" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="68.77" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="68.77" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="68.77" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="K18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="68.77" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="K19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="68.77" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="23"/>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="K20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="68.77" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K21" s="27"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="68.77" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -4971,6 +4971,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
 </worksheet>
 </file>